--- a/Proiect/Proiect/Cleaned Data/theft_cleaned.xlsx
+++ b/Proiect/Proiect/Cleaned Data/theft_cleaned.xlsx
@@ -14,21 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Tara</t>
   </si>
   <si>
     <t>2023</t>
@@ -55,9 +43,15 @@
     <t>Denmark</t>
   </si>
   <si>
+    <t>Estonia</t>
+  </si>
+  <si>
     <t>Finland</t>
   </si>
   <si>
+    <t>France</t>
+  </si>
+  <si>
     <t>Germany</t>
   </si>
   <si>
@@ -73,6 +67,9 @@
     <t>Ireland</t>
   </si>
   <si>
+    <t>Italy</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
@@ -85,7 +82,13 @@
     <t>Malta</t>
   </si>
   <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
     <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Norway</t>
   </si>
   <si>
     <t>Poland</t>
@@ -467,546 +470,262 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2">
+        <v>110359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3">
+        <v>205003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4">
+        <v>26153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B5">
+        <v>11270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>115423</v>
-      </c>
-      <c r="C2">
-        <v>84734</v>
-      </c>
-      <c r="D2">
-        <v>73213</v>
-      </c>
-      <c r="E2">
-        <v>97139</v>
-      </c>
-      <c r="F2">
-        <v>110359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B6">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>227402</v>
-      </c>
-      <c r="C3">
-        <v>157190</v>
-      </c>
-      <c r="D3">
-        <v>167303</v>
-      </c>
-      <c r="E3">
-        <v>199703</v>
-      </c>
-      <c r="F3">
-        <v>205003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B7">
+        <v>35373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>33172</v>
-      </c>
-      <c r="C4">
-        <v>27036</v>
-      </c>
-      <c r="D4">
-        <v>24435</v>
-      </c>
-      <c r="E4">
-        <v>28250</v>
-      </c>
-      <c r="F4">
-        <v>26153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B8">
+        <v>158491</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>11862</v>
-      </c>
-      <c r="C5">
-        <v>10418</v>
-      </c>
-      <c r="D5">
-        <v>10325</v>
-      </c>
-      <c r="E5">
-        <v>11087</v>
-      </c>
-      <c r="F5">
-        <v>11270</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B9">
+        <v>9699</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>642</v>
-      </c>
-      <c r="C6">
-        <v>513</v>
-      </c>
-      <c r="D6">
-        <v>527</v>
-      </c>
-      <c r="E6">
-        <v>613</v>
-      </c>
-      <c r="F6">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B10">
+        <v>126722</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>59850</v>
-      </c>
-      <c r="C7">
-        <v>45638</v>
-      </c>
-      <c r="D7">
-        <v>26928</v>
-      </c>
-      <c r="E7">
-        <v>34774</v>
-      </c>
-      <c r="F7">
-        <v>35373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B11">
+        <v>1359102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>170043</v>
-      </c>
-      <c r="C8">
-        <v>142042</v>
-      </c>
-      <c r="D8">
-        <v>124628</v>
-      </c>
-      <c r="E8">
-        <v>146613</v>
-      </c>
-      <c r="F8">
-        <v>158491</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B12">
+        <v>1172337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
-        <v>122731</v>
-      </c>
-      <c r="C9">
-        <v>134831</v>
-      </c>
-      <c r="D9">
-        <v>124104</v>
-      </c>
-      <c r="E9">
-        <v>124826</v>
-      </c>
-      <c r="F9">
-        <v>126722</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="B13">
+        <v>68659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
-        <v>1025321</v>
-      </c>
-      <c r="C10">
-        <v>931793</v>
-      </c>
-      <c r="D10">
-        <v>835368</v>
-      </c>
-      <c r="E10">
-        <v>1043887</v>
-      </c>
-      <c r="F10">
-        <v>1172337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="B14">
+        <v>50934</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
-        <v>85825</v>
-      </c>
-      <c r="C11">
-        <v>60947</v>
-      </c>
-      <c r="D11">
-        <v>58937</v>
-      </c>
-      <c r="E11">
-        <v>71130</v>
-      </c>
-      <c r="F11">
-        <v>68659</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="B15">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
-        <v>56967</v>
-      </c>
-      <c r="C12">
-        <v>50441</v>
-      </c>
-      <c r="D12">
-        <v>42428</v>
-      </c>
-      <c r="E12">
-        <v>48616</v>
-      </c>
-      <c r="F12">
-        <v>50934</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="B16">
+        <v>69354</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
-        <v>3476</v>
-      </c>
-      <c r="C13">
-        <v>3503</v>
-      </c>
-      <c r="D13">
-        <v>3760</v>
-      </c>
-      <c r="E13">
-        <v>3414</v>
-      </c>
-      <c r="F13">
-        <v>3629</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="B17">
+        <v>888340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
-        <v>65405</v>
-      </c>
-      <c r="C14">
-        <v>48830</v>
-      </c>
-      <c r="D14">
-        <v>44573</v>
-      </c>
-      <c r="E14">
-        <v>62355</v>
-      </c>
-      <c r="F14">
-        <v>69354</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B18">
+        <v>10712</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
-        <v>13111</v>
-      </c>
-      <c r="C15">
-        <v>12799</v>
-      </c>
-      <c r="D15">
-        <v>7900</v>
-      </c>
-      <c r="E15">
-        <v>9621</v>
-      </c>
-      <c r="F15">
-        <v>10712</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="B19">
+        <v>10094</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
-        <v>10902</v>
-      </c>
-      <c r="C16">
-        <v>9447</v>
-      </c>
-      <c r="D16">
-        <v>7736</v>
-      </c>
-      <c r="E16">
-        <v>9628</v>
-      </c>
-      <c r="F16">
-        <v>10094</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="B20">
+        <v>22268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
-        <v>9925</v>
-      </c>
-      <c r="C17">
-        <v>9258</v>
-      </c>
-      <c r="D17">
-        <v>10902</v>
-      </c>
-      <c r="E17">
-        <v>16264</v>
-      </c>
-      <c r="F17">
-        <v>22268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="B21">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
-        <v>5187</v>
-      </c>
-      <c r="C18">
-        <v>3414</v>
-      </c>
-      <c r="D18">
-        <v>3504</v>
-      </c>
-      <c r="E18">
-        <v>3584</v>
-      </c>
-      <c r="F18">
-        <v>3716</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="B22">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
-        <v>233860</v>
-      </c>
-      <c r="C19">
-        <v>204740</v>
-      </c>
-      <c r="D19">
-        <v>183940</v>
-      </c>
-      <c r="E19">
-        <v>232960</v>
-      </c>
-      <c r="F19">
+      <c r="B23">
         <v>245460</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
-        <v>102585</v>
-      </c>
-      <c r="C20">
-        <v>98519</v>
-      </c>
-      <c r="D20">
-        <v>108720</v>
-      </c>
-      <c r="E20">
-        <v>120901</v>
-      </c>
-      <c r="F20">
+      <c r="B24">
+        <v>110995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
         <v>117183</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21">
-        <v>82120</v>
-      </c>
-      <c r="C21">
-        <v>65159</v>
-      </c>
-      <c r="D21">
-        <v>63954</v>
-      </c>
-      <c r="E21">
-        <v>73365</v>
-      </c>
-      <c r="F21">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
         <v>75123</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
-        <v>66801</v>
-      </c>
-      <c r="C22">
-        <v>62077</v>
-      </c>
-      <c r="D22">
-        <v>64509</v>
-      </c>
-      <c r="E22">
-        <v>59293</v>
-      </c>
-      <c r="F22">
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
         <v>63734</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23">
-        <v>14796</v>
-      </c>
-      <c r="C23">
-        <v>14003</v>
-      </c>
-      <c r="D23">
-        <v>9799</v>
-      </c>
-      <c r="E23">
-        <v>11217</v>
-      </c>
-      <c r="F23">
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
         <v>11826</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24">
-        <v>26283</v>
-      </c>
-      <c r="C24">
-        <v>24429</v>
-      </c>
-      <c r="D24">
-        <v>18134</v>
-      </c>
-      <c r="E24">
-        <v>21551</v>
-      </c>
-      <c r="F24">
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
         <v>24895</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25">
-        <v>204771</v>
-      </c>
-      <c r="C25">
-        <v>124467</v>
-      </c>
-      <c r="D25">
-        <v>144594</v>
-      </c>
-      <c r="E25">
-        <v>205730</v>
-      </c>
-      <c r="F25">
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
         <v>222334</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26">
-        <v>329054</v>
-      </c>
-      <c r="C26">
-        <v>311038</v>
-      </c>
-      <c r="D26">
-        <v>288987</v>
-      </c>
-      <c r="E26">
-        <v>298778</v>
-      </c>
-      <c r="F26">
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
         <v>287940</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>132646</v>
-      </c>
-      <c r="C27">
-        <v>121322</v>
-      </c>
-      <c r="D27">
-        <v>117586</v>
-      </c>
-      <c r="E27">
-        <v>138970</v>
-      </c>
-      <c r="F27">
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
         <v>168575</v>
       </c>
     </row>

--- a/Proiect/Proiect/Cleaned Data/theft_cleaned.xlsx
+++ b/Proiect/Proiect/Cleaned Data/theft_cleaned.xlsx
@@ -14,20 +14,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Tara</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
+    <t>Albania</t>
+  </si>
+  <si>
     <t>Austria</t>
   </si>
   <si>
     <t>Belgium</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
     <t>Bulgaria</t>
   </si>
   <si>
@@ -70,9 +88,15 @@
     <t>Italy</t>
   </si>
   <si>
+    <t>Kosovo*</t>
+  </si>
+  <si>
     <t>Latvia</t>
   </si>
   <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -82,12 +106,18 @@
     <t>Malta</t>
   </si>
   <si>
+    <t>Moldova</t>
+  </si>
+  <si>
     <t>Montenegro</t>
   </si>
   <si>
     <t>Netherlands</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>Norway</t>
   </si>
   <si>
@@ -100,6 +130,9 @@
     <t>Romania</t>
   </si>
   <si>
+    <t>Serbia</t>
+  </si>
+  <si>
     <t>Slovakia</t>
   </si>
   <si>
@@ -113,6 +146,12 @@
   </si>
   <si>
     <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -470,263 +509,827 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2">
+        <v>4833</v>
+      </c>
+      <c r="C2">
+        <v>3162</v>
+      </c>
+      <c r="D2">
+        <v>3342</v>
+      </c>
+      <c r="E2">
+        <v>2458</v>
+      </c>
+      <c r="F2">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>115423</v>
+      </c>
+      <c r="C3">
+        <v>84734</v>
+      </c>
+      <c r="D3">
+        <v>73213</v>
+      </c>
+      <c r="E3">
+        <v>97139</v>
+      </c>
+      <c r="F3">
         <v>110359</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>227402</v>
+      </c>
+      <c r="C4">
+        <v>157190</v>
+      </c>
+      <c r="D4">
+        <v>167303</v>
+      </c>
+      <c r="E4">
+        <v>199703</v>
+      </c>
+      <c r="F4">
         <v>205003</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>3718</v>
+      </c>
+      <c r="C5">
+        <v>3669</v>
+      </c>
+      <c r="D5">
+        <v>3161</v>
+      </c>
+      <c r="E5">
+        <v>3087</v>
+      </c>
+      <c r="F5">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>33172</v>
+      </c>
+      <c r="C6">
+        <v>27036</v>
+      </c>
+      <c r="D6">
+        <v>24435</v>
+      </c>
+      <c r="E6">
+        <v>28250</v>
+      </c>
+      <c r="F6">
         <v>26153</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>11862</v>
+      </c>
+      <c r="C7">
+        <v>10418</v>
+      </c>
+      <c r="D7">
+        <v>10325</v>
+      </c>
+      <c r="E7">
+        <v>11087</v>
+      </c>
+      <c r="F7">
         <v>11270</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>642</v>
+      </c>
+      <c r="C8">
+        <v>513</v>
+      </c>
+      <c r="D8">
+        <v>527</v>
+      </c>
+      <c r="E8">
+        <v>613</v>
+      </c>
+      <c r="F8">
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>59850</v>
+      </c>
+      <c r="C9">
+        <v>45638</v>
+      </c>
+      <c r="D9">
+        <v>26928</v>
+      </c>
+      <c r="E9">
+        <v>34774</v>
+      </c>
+      <c r="F9">
         <v>35373</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>170043</v>
+      </c>
+      <c r="C10">
+        <v>142042</v>
+      </c>
+      <c r="D10">
+        <v>124628</v>
+      </c>
+      <c r="E10">
+        <v>146613</v>
+      </c>
+      <c r="F10">
         <v>158491</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>6804</v>
+      </c>
+      <c r="C11">
+        <v>6863</v>
+      </c>
+      <c r="D11">
+        <v>7513</v>
+      </c>
+      <c r="E11">
+        <v>8027</v>
+      </c>
+      <c r="F11">
         <v>9699</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>122731</v>
+      </c>
+      <c r="C12">
+        <v>134831</v>
+      </c>
+      <c r="D12">
+        <v>124104</v>
+      </c>
+      <c r="E12">
+        <v>124826</v>
+      </c>
+      <c r="F12">
         <v>126722</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>1440130</v>
+      </c>
+      <c r="C13">
+        <v>1174223</v>
+      </c>
+      <c r="D13">
+        <v>1208310</v>
+      </c>
+      <c r="E13">
+        <v>1358091</v>
+      </c>
+      <c r="F13">
         <v>1359102</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>1025321</v>
+      </c>
+      <c r="C14">
+        <v>931793</v>
+      </c>
+      <c r="D14">
+        <v>835368</v>
+      </c>
+      <c r="E14">
+        <v>1043887</v>
+      </c>
+      <c r="F14">
         <v>1172337</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>85825</v>
+      </c>
+      <c r="C15">
+        <v>60947</v>
+      </c>
+      <c r="D15">
+        <v>58937</v>
+      </c>
+      <c r="E15">
+        <v>71130</v>
+      </c>
+      <c r="F15">
         <v>68659</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>56967</v>
+      </c>
+      <c r="C16">
+        <v>50441</v>
+      </c>
+      <c r="D16">
+        <v>42428</v>
+      </c>
+      <c r="E16">
+        <v>48616</v>
+      </c>
+      <c r="F16">
         <v>50934</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>3476</v>
+      </c>
+      <c r="C17">
+        <v>3503</v>
+      </c>
+      <c r="D17">
+        <v>3760</v>
+      </c>
+      <c r="E17">
+        <v>3414</v>
+      </c>
+      <c r="F17">
         <v>3629</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>65405</v>
+      </c>
+      <c r="C18">
+        <v>48830</v>
+      </c>
+      <c r="D18">
+        <v>44573</v>
+      </c>
+      <c r="E18">
+        <v>62355</v>
+      </c>
+      <c r="F18">
         <v>69354</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>906552</v>
+      </c>
+      <c r="C19">
+        <v>612230</v>
+      </c>
+      <c r="D19">
+        <v>701154</v>
+      </c>
+      <c r="E19">
+        <v>844086</v>
+      </c>
+      <c r="F19">
         <v>888340</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>4835</v>
+      </c>
+      <c r="C20">
+        <v>4224</v>
+      </c>
+      <c r="D20">
+        <v>4621</v>
+      </c>
+      <c r="E20">
+        <v>4621</v>
+      </c>
+      <c r="F20">
+        <v>4621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>13111</v>
+      </c>
+      <c r="C21">
+        <v>12799</v>
+      </c>
+      <c r="D21">
+        <v>7900</v>
+      </c>
+      <c r="E21">
+        <v>9621</v>
+      </c>
+      <c r="F21">
         <v>10712</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>178</v>
+      </c>
+      <c r="C22">
+        <v>133</v>
+      </c>
+      <c r="D22">
+        <v>184</v>
+      </c>
+      <c r="E22">
+        <v>254</v>
+      </c>
+      <c r="F22">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>10902</v>
+      </c>
+      <c r="C23">
+        <v>9447</v>
+      </c>
+      <c r="D23">
+        <v>7736</v>
+      </c>
+      <c r="E23">
+        <v>9628</v>
+      </c>
+      <c r="F23">
         <v>10094</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>9925</v>
+      </c>
+      <c r="C24">
+        <v>9258</v>
+      </c>
+      <c r="D24">
+        <v>10902</v>
+      </c>
+      <c r="E24">
+        <v>16264</v>
+      </c>
+      <c r="F24">
         <v>22268</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25">
+        <v>5187</v>
+      </c>
+      <c r="C25">
+        <v>3414</v>
+      </c>
+      <c r="D25">
+        <v>3504</v>
+      </c>
+      <c r="E25">
+        <v>3584</v>
+      </c>
+      <c r="F25">
         <v>3716</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>159643.0540540541</v>
+      </c>
+      <c r="C26">
+        <v>131434</v>
+      </c>
+      <c r="D26">
+        <v>129781.1351351351</v>
+      </c>
+      <c r="E26">
+        <v>152815.4864864865</v>
+      </c>
+      <c r="F26">
+        <v>158862.3513513514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>413</v>
+      </c>
+      <c r="C27">
+        <v>320</v>
+      </c>
+      <c r="D27">
+        <v>337</v>
+      </c>
+      <c r="E27">
+        <v>340</v>
+      </c>
+      <c r="F27">
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>233860</v>
+      </c>
+      <c r="C28">
+        <v>204740</v>
+      </c>
+      <c r="D28">
+        <v>183940</v>
+      </c>
+      <c r="E28">
+        <v>232960</v>
+      </c>
+      <c r="F28">
         <v>245460</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>159643.0540540541</v>
+      </c>
+      <c r="C29">
+        <v>131434</v>
+      </c>
+      <c r="D29">
+        <v>129781.1351351351</v>
+      </c>
+      <c r="E29">
+        <v>152815.4864864865</v>
+      </c>
+      <c r="F29">
+        <v>158862.3513513514</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>94544</v>
+      </c>
+      <c r="C30">
+        <v>86519</v>
+      </c>
+      <c r="D30">
+        <v>79133</v>
+      </c>
+      <c r="E30">
+        <v>99312</v>
+      </c>
+      <c r="F30">
         <v>110995</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25">
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>102585</v>
+      </c>
+      <c r="C31">
+        <v>98519</v>
+      </c>
+      <c r="D31">
+        <v>108720</v>
+      </c>
+      <c r="E31">
+        <v>120901</v>
+      </c>
+      <c r="F31">
         <v>117183</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26">
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>82120</v>
+      </c>
+      <c r="C32">
+        <v>65159</v>
+      </c>
+      <c r="D32">
+        <v>63954</v>
+      </c>
+      <c r="E32">
+        <v>73365</v>
+      </c>
+      <c r="F32">
         <v>75123</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27">
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>66801</v>
+      </c>
+      <c r="C33">
+        <v>62077</v>
+      </c>
+      <c r="D33">
+        <v>64509</v>
+      </c>
+      <c r="E33">
+        <v>59293</v>
+      </c>
+      <c r="F33">
         <v>63734</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>18072</v>
+      </c>
+      <c r="C34">
+        <v>15228</v>
+      </c>
+      <c r="D34">
+        <v>17363</v>
+      </c>
+      <c r="E34">
+        <v>17580</v>
+      </c>
+      <c r="F34">
+        <v>14783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>14796</v>
+      </c>
+      <c r="C35">
+        <v>14003</v>
+      </c>
+      <c r="D35">
+        <v>9799</v>
+      </c>
+      <c r="E35">
+        <v>11217</v>
+      </c>
+      <c r="F35">
         <v>11826</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>26283</v>
+      </c>
+      <c r="C36">
+        <v>24429</v>
+      </c>
+      <c r="D36">
+        <v>18134</v>
+      </c>
+      <c r="E36">
+        <v>21551</v>
+      </c>
+      <c r="F36">
         <v>24895</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>204771</v>
+      </c>
+      <c r="C37">
+        <v>124467</v>
+      </c>
+      <c r="D37">
+        <v>144594</v>
+      </c>
+      <c r="E37">
+        <v>205730</v>
+      </c>
+      <c r="F37">
         <v>222334</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>329054</v>
+      </c>
+      <c r="C38">
+        <v>311038</v>
+      </c>
+      <c r="D38">
+        <v>288987</v>
+      </c>
+      <c r="E38">
+        <v>298778</v>
+      </c>
+      <c r="F38">
         <v>287940</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39">
+        <v>132646</v>
+      </c>
+      <c r="C39">
+        <v>121322</v>
+      </c>
+      <c r="D39">
+        <v>117586</v>
+      </c>
+      <c r="E39">
+        <v>138970</v>
+      </c>
+      <c r="F39">
         <v>168575</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40">
+        <v>216554</v>
+      </c>
+      <c r="C40">
+        <v>197899</v>
+      </c>
+      <c r="D40">
+        <v>209990</v>
+      </c>
+      <c r="E40">
+        <v>242048</v>
+      </c>
+      <c r="F40">
+        <v>181636</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
+        <v>159643.0540540541</v>
+      </c>
+      <c r="C41">
+        <v>131434</v>
+      </c>
+      <c r="D41">
+        <v>129781.1351351351</v>
+      </c>
+      <c r="E41">
+        <v>152815.4864864865</v>
+      </c>
+      <c r="F41">
+        <v>158862.3513513514</v>
       </c>
     </row>
   </sheetData>
